--- a/processed_data/hard_data_exports/hunt_tables/2026/2026_SHEEP_ROCKY_MOUNTAIN_EWE.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/2026_SHEEP_ROCKY_MOUNTAIN_EWE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_sheep_rocky_mountain_ewe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026_sheep_rocky_mountain_ewe" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_sheep_rocky_mountain_ewe'!$A$3:$J$4</definedName>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.95" customWidth="1" min="1" max="1"/>
@@ -603,6 +603,26 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Success (Prior Year %)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Average Harvest Age (Prior Year)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Average Days Hunted (Prior Year)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -653,6 +673,20 @@
       <c r="J4" s="6" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
